--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F51EE9-A1E0-4645-9B99-B88AA439DB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1147D176-8EA1-574B-B410-37770142ADC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="500" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="760" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="1501">
   <si>
     <t>Name</t>
   </si>
@@ -4522,6 +4522,15 @@
   </si>
   <si>
     <t>https://www.geonames.org/2761164/wilten.html</t>
+  </si>
+  <si>
+    <t>St. Lorenz Strom</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/6156984/st-lawrence-river.html</t>
+  </si>
+  <si>
+    <t>SanktLorenzStrom</t>
   </si>
 </sst>
 </file>
@@ -4943,7 +4952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5221,6 +5230,7 @@
     <xf numFmtId="0" fontId="35" fillId="13" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -5271,9 +5281,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D563" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D562">
-    <sortCondition ref="D562"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D564" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D563">
+    <sortCondition ref="D563"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -5483,7 +5493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Y1426"/>
+  <dimension ref="A2:Y1427"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -21242,14 +21252,14 @@
     </row>
     <row r="469" spans="1:25" ht="15.75" customHeight="1">
       <c r="A469" s="13" t="s">
-        <v>1150</v>
+        <v>1498</v>
       </c>
       <c r="B469" s="13"/>
-      <c r="C469" s="86" t="s">
-        <v>1151</v>
+      <c r="C469" s="111" t="s">
+        <v>1499</v>
       </c>
       <c r="D469" s="13" t="s">
-        <v>1152</v>
+        <v>1500</v>
       </c>
       <c r="E469" s="1"/>
       <c r="F469" s="1"/>
@@ -21274,15 +21284,15 @@
       <c r="Y469" s="1"/>
     </row>
     <row r="470" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A470" s="90" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B470" s="90"/>
-      <c r="C470" s="91" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D470" s="90" t="s">
-        <v>1434</v>
+      <c r="A470" s="13" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B470" s="13"/>
+      <c r="C470" s="86" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D470" s="13" t="s">
+        <v>1152</v>
       </c>
       <c r="E470" s="1"/>
       <c r="F470" s="1"/>
@@ -21307,17 +21317,15 @@
       <c r="Y470" s="1"/>
     </row>
     <row r="471" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A471" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B471" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C471" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D471" s="7" t="s">
-        <v>668</v>
+      <c r="A471" s="90" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B471" s="90"/>
+      <c r="C471" s="91" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D471" s="90" t="s">
+        <v>1434</v>
       </c>
       <c r="E471" s="1"/>
       <c r="F471" s="1"/>
@@ -21342,15 +21350,17 @@
       <c r="Y471" s="1"/>
     </row>
     <row r="472" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A472" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="B472" s="9"/>
-      <c r="C472" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="D472" s="9" t="s">
-        <v>671</v>
+      <c r="A472" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C472" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D472" s="7" t="s">
+        <v>668</v>
       </c>
       <c r="E472" s="1"/>
       <c r="F472" s="1"/>
@@ -21376,14 +21386,14 @@
     </row>
     <row r="473" spans="1:25" ht="15.75" customHeight="1">
       <c r="A473" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="B473" s="9"/>
-      <c r="C473" s="10" t="s">
-        <v>689</v>
+      <c r="C473" s="11" t="s">
+        <v>672</v>
       </c>
       <c r="D473" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="E473" s="1"/>
       <c r="F473" s="1"/>
@@ -21408,17 +21418,15 @@
       <c r="Y473" s="1"/>
     </row>
     <row r="474" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A474" s="90" t="s">
-        <v>1435</v>
-      </c>
-      <c r="B474" s="90" t="s">
-        <v>1436</v>
-      </c>
-      <c r="C474" s="91" t="s">
-        <v>1437</v>
-      </c>
-      <c r="D474" s="90" t="s">
-        <v>1435</v>
+      <c r="A474" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B474" s="9"/>
+      <c r="C474" s="10" t="s">
+        <v>689</v>
+      </c>
+      <c r="D474" s="9" t="s">
+        <v>688</v>
       </c>
       <c r="E474" s="1"/>
       <c r="F474" s="1"/>
@@ -21442,84 +21450,86 @@
       <c r="X474" s="1"/>
       <c r="Y474" s="1"/>
     </row>
-    <row r="475" spans="1:25" s="99" customFormat="1" ht="15.75" customHeight="1">
+    <row r="475" spans="1:25" ht="15.75" customHeight="1">
       <c r="A475" s="90" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B475" s="90" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C475" s="91" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D475" s="90" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E475" s="1"/>
+      <c r="F475" s="1"/>
+      <c r="G475" s="1"/>
+      <c r="H475" s="1"/>
+      <c r="I475" s="1"/>
+      <c r="J475" s="1"/>
+      <c r="K475" s="1"/>
+      <c r="L475" s="1"/>
+      <c r="M475" s="1"/>
+      <c r="N475" s="1"/>
+      <c r="O475" s="1"/>
+      <c r="P475" s="1"/>
+      <c r="Q475" s="1"/>
+      <c r="R475" s="1"/>
+      <c r="S475" s="1"/>
+      <c r="T475" s="1"/>
+      <c r="U475" s="1"/>
+      <c r="V475" s="1"/>
+      <c r="W475" s="1"/>
+      <c r="X475" s="1"/>
+      <c r="Y475" s="1"/>
+    </row>
+    <row r="476" spans="1:25" s="99" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A476" s="90" t="s">
         <v>1477</v>
       </c>
-      <c r="B475" s="90"/>
-      <c r="C475" s="91" t="s">
+      <c r="B476" s="90"/>
+      <c r="C476" s="91" t="s">
         <v>1478</v>
       </c>
-      <c r="D475" s="90" t="s">
+      <c r="D476" s="90" t="s">
         <v>1479</v>
       </c>
-      <c r="E475" s="98"/>
-      <c r="F475" s="98"/>
-      <c r="G475" s="98"/>
-      <c r="H475" s="98"/>
-      <c r="I475" s="98"/>
-      <c r="J475" s="98"/>
-      <c r="K475" s="98"/>
-      <c r="L475" s="98"/>
-      <c r="M475" s="98"/>
-      <c r="N475" s="98"/>
-      <c r="O475" s="98"/>
-      <c r="P475" s="98"/>
-      <c r="Q475" s="98"/>
-      <c r="R475" s="98"/>
-      <c r="S475" s="98"/>
-      <c r="T475" s="98"/>
-      <c r="U475" s="98"/>
-      <c r="V475" s="98"/>
-      <c r="W475" s="98"/>
-      <c r="X475" s="98"/>
-      <c r="Y475" s="98"/>
-    </row>
-    <row r="476" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A476" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B476" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C476" s="11" t="s">
-        <v>692</v>
-      </c>
-      <c r="D476" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="E476" s="1"/>
-      <c r="F476" s="1"/>
-      <c r="G476" s="1"/>
-      <c r="H476" s="1"/>
-      <c r="I476" s="1"/>
-      <c r="J476" s="1"/>
-      <c r="K476" s="1"/>
-      <c r="L476" s="1"/>
-      <c r="M476" s="1"/>
-      <c r="N476" s="1"/>
-      <c r="O476" s="1"/>
-      <c r="P476" s="1"/>
-      <c r="Q476" s="1"/>
-      <c r="R476" s="1"/>
-      <c r="S476" s="1"/>
-      <c r="T476" s="1"/>
-      <c r="U476" s="1"/>
-      <c r="V476" s="1"/>
-      <c r="W476" s="1"/>
-      <c r="X476" s="1"/>
-      <c r="Y476" s="1"/>
+      <c r="E476" s="98"/>
+      <c r="F476" s="98"/>
+      <c r="G476" s="98"/>
+      <c r="H476" s="98"/>
+      <c r="I476" s="98"/>
+      <c r="J476" s="98"/>
+      <c r="K476" s="98"/>
+      <c r="L476" s="98"/>
+      <c r="M476" s="98"/>
+      <c r="N476" s="98"/>
+      <c r="O476" s="98"/>
+      <c r="P476" s="98"/>
+      <c r="Q476" s="98"/>
+      <c r="R476" s="98"/>
+      <c r="S476" s="98"/>
+      <c r="T476" s="98"/>
+      <c r="U476" s="98"/>
+      <c r="V476" s="98"/>
+      <c r="W476" s="98"/>
+      <c r="X476" s="98"/>
+      <c r="Y476" s="98"/>
     </row>
     <row r="477" spans="1:25" ht="15.75" customHeight="1">
       <c r="A477" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B477" s="9"/>
-      <c r="C477" s="10" t="s">
-        <v>844</v>
+        <v>690</v>
+      </c>
+      <c r="B477" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C477" s="11" t="s">
+        <v>692</v>
       </c>
       <c r="D477" s="9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E477" s="1"/>
       <c r="F477" s="1"/>
@@ -21544,17 +21554,15 @@
       <c r="Y477" s="1"/>
     </row>
     <row r="478" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A478" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B478" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C478" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D478" s="1" t="s">
-        <v>1009</v>
+      <c r="A478" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B478" s="9"/>
+      <c r="C478" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="D478" s="9" t="s">
+        <v>695</v>
       </c>
       <c r="E478" s="1"/>
       <c r="F478" s="1"/>
@@ -21579,15 +21587,17 @@
       <c r="Y478" s="1"/>
     </row>
     <row r="479" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A479" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B479" s="13"/>
-      <c r="C479" s="22" t="s">
-        <v>697</v>
-      </c>
-      <c r="D479" s="13" t="s">
-        <v>696</v>
+      <c r="A479" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B479" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D479" s="1" t="s">
+        <v>1009</v>
       </c>
       <c r="E479" s="1"/>
       <c r="F479" s="1"/>
@@ -21613,51 +21623,49 @@
     </row>
     <row r="480" spans="1:25" ht="15.75" customHeight="1">
       <c r="A480" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="B480" s="13"/>
+      <c r="C480" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D480" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="E480" s="1"/>
+      <c r="F480" s="1"/>
+      <c r="G480" s="1"/>
+      <c r="H480" s="1"/>
+      <c r="I480" s="1"/>
+      <c r="J480" s="1"/>
+      <c r="K480" s="1"/>
+      <c r="L480" s="1"/>
+      <c r="M480" s="1"/>
+      <c r="N480" s="1"/>
+      <c r="O480" s="1"/>
+      <c r="P480" s="1"/>
+      <c r="Q480" s="1"/>
+      <c r="R480" s="1"/>
+      <c r="S480" s="1"/>
+      <c r="T480" s="1"/>
+      <c r="U480" s="1"/>
+      <c r="V480" s="1"/>
+      <c r="W480" s="1"/>
+      <c r="X480" s="1"/>
+      <c r="Y480" s="1"/>
+    </row>
+    <row r="481" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A481" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="B480" s="13" t="s">
+      <c r="B481" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="C480" s="14" t="s">
+      <c r="C481" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="D480" s="13" t="s">
+      <c r="D481" s="13" t="s">
         <v>698</v>
-      </c>
-      <c r="E480" s="2"/>
-      <c r="F480" s="2"/>
-      <c r="G480" s="2"/>
-      <c r="H480" s="2"/>
-      <c r="I480" s="2"/>
-      <c r="J480" s="2"/>
-      <c r="K480" s="2"/>
-      <c r="L480" s="2"/>
-      <c r="M480" s="2"/>
-      <c r="N480" s="2"/>
-      <c r="O480" s="2"/>
-      <c r="P480" s="2"/>
-      <c r="Q480" s="2"/>
-      <c r="R480" s="2"/>
-      <c r="S480" s="2"/>
-      <c r="T480" s="2"/>
-      <c r="U480" s="2"/>
-      <c r="V480" s="2"/>
-      <c r="W480" s="2"/>
-      <c r="X480" s="2"/>
-      <c r="Y480" s="2"/>
-    </row>
-    <row r="481" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A481" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B481" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="C481" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D481" s="9" t="s">
-        <v>701</v>
       </c>
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
@@ -21682,52 +21690,52 @@
       <c r="Y481" s="2"/>
     </row>
     <row r="482" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A482" s="3" t="s">
+      <c r="A482" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B482" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C482" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D482" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="E482" s="2"/>
+      <c r="F482" s="2"/>
+      <c r="G482" s="2"/>
+      <c r="H482" s="2"/>
+      <c r="I482" s="2"/>
+      <c r="J482" s="2"/>
+      <c r="K482" s="2"/>
+      <c r="L482" s="2"/>
+      <c r="M482" s="2"/>
+      <c r="N482" s="2"/>
+      <c r="O482" s="2"/>
+      <c r="P482" s="2"/>
+      <c r="Q482" s="2"/>
+      <c r="R482" s="2"/>
+      <c r="S482" s="2"/>
+      <c r="T482" s="2"/>
+      <c r="U482" s="2"/>
+      <c r="V482" s="2"/>
+      <c r="W482" s="2"/>
+      <c r="X482" s="2"/>
+      <c r="Y482" s="2"/>
+    </row>
+    <row r="483" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A483" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="B482" s="3" t="s">
+      <c r="B483" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="C482" s="3" t="s">
+      <c r="C483" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="D482" s="1" t="s">
+      <c r="D483" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="E482" s="1"/>
-      <c r="F482" s="1"/>
-      <c r="G482" s="1"/>
-      <c r="H482" s="1"/>
-      <c r="I482" s="1"/>
-      <c r="J482" s="1"/>
-      <c r="K482" s="1"/>
-      <c r="L482" s="1"/>
-      <c r="M482" s="1"/>
-      <c r="N482" s="1"/>
-      <c r="O482" s="1"/>
-      <c r="P482" s="1"/>
-      <c r="Q482" s="1"/>
-      <c r="R482" s="1"/>
-      <c r="S482" s="1"/>
-      <c r="T482" s="1"/>
-      <c r="U482" s="1"/>
-      <c r="V482" s="1"/>
-      <c r="W482" s="1"/>
-      <c r="X482" s="1"/>
-      <c r="Y482" s="1"/>
-    </row>
-    <row r="483" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A483" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="B483" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="C483" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D483" s="9" t="s">
-        <v>704</v>
       </c>
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
@@ -21753,14 +21761,16 @@
     </row>
     <row r="484" spans="1:25" ht="15.75" customHeight="1">
       <c r="A484" s="9" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B484" s="9"/>
+        <v>704</v>
+      </c>
+      <c r="B484" s="9" t="s">
+        <v>705</v>
+      </c>
       <c r="C484" s="10" t="s">
-        <v>1290</v>
+        <v>706</v>
       </c>
       <c r="D484" s="9" t="s">
-        <v>1289</v>
+        <v>704</v>
       </c>
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
@@ -21786,14 +21796,14 @@
     </row>
     <row r="485" spans="1:25" ht="15.75" customHeight="1">
       <c r="A485" s="9" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B485" s="9"/>
       <c r="C485" s="10" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D485" s="9" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E485" s="1"/>
       <c r="F485" s="1"/>
@@ -21818,52 +21828,50 @@
       <c r="Y485" s="1"/>
     </row>
     <row r="486" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A486" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="B486" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C486" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="D486" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E486" s="2"/>
-      <c r="F486" s="2"/>
-      <c r="G486" s="2"/>
-      <c r="H486" s="2"/>
-      <c r="I486" s="2"/>
-      <c r="J486" s="2"/>
-      <c r="K486" s="2"/>
-      <c r="L486" s="2"/>
-      <c r="M486" s="2"/>
-      <c r="N486" s="2"/>
-      <c r="O486" s="2"/>
-      <c r="P486" s="2"/>
-      <c r="Q486" s="2"/>
-      <c r="R486" s="2"/>
-      <c r="S486" s="2"/>
-      <c r="T486" s="2"/>
-      <c r="U486" s="2"/>
-      <c r="V486" s="2"/>
-      <c r="W486" s="2"/>
-      <c r="X486" s="2"/>
-      <c r="Y486" s="2"/>
+      <c r="A486" s="9" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B486" s="9"/>
+      <c r="C486" s="10" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D486" s="9" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E486" s="1"/>
+      <c r="F486" s="1"/>
+      <c r="G486" s="1"/>
+      <c r="H486" s="1"/>
+      <c r="I486" s="1"/>
+      <c r="J486" s="1"/>
+      <c r="K486" s="1"/>
+      <c r="L486" s="1"/>
+      <c r="M486" s="1"/>
+      <c r="N486" s="1"/>
+      <c r="O486" s="1"/>
+      <c r="P486" s="1"/>
+      <c r="Q486" s="1"/>
+      <c r="R486" s="1"/>
+      <c r="S486" s="1"/>
+      <c r="T486" s="1"/>
+      <c r="U486" s="1"/>
+      <c r="V486" s="1"/>
+      <c r="W486" s="1"/>
+      <c r="X486" s="1"/>
+      <c r="Y486" s="1"/>
     </row>
     <row r="487" spans="1:25" ht="15.75" customHeight="1">
       <c r="A487" s="3" t="s">
-        <v>1153</v>
+        <v>707</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1154</v>
+        <v>708</v>
       </c>
       <c r="C487" s="3" t="s">
-        <v>1155</v>
+        <v>709</v>
       </c>
       <c r="D487" s="3" t="s">
-        <v>1153</v>
+        <v>707</v>
       </c>
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
@@ -21889,16 +21897,16 @@
     </row>
     <row r="488" spans="1:25" ht="15.75" customHeight="1">
       <c r="A488" s="3" t="s">
-        <v>1472</v>
+        <v>1153</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1473</v>
-      </c>
-      <c r="C488" s="50" t="s">
-        <v>1474</v>
+        <v>1154</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>1155</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>1472</v>
+        <v>1153</v>
       </c>
       <c r="E488" s="2"/>
       <c r="F488" s="2"/>
@@ -21924,51 +21932,51 @@
     </row>
     <row r="489" spans="1:25" ht="15.75" customHeight="1">
       <c r="A489" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C489" s="50" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D489" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E489" s="2"/>
+      <c r="F489" s="2"/>
+      <c r="G489" s="2"/>
+      <c r="H489" s="2"/>
+      <c r="I489" s="2"/>
+      <c r="J489" s="2"/>
+      <c r="K489" s="2"/>
+      <c r="L489" s="2"/>
+      <c r="M489" s="2"/>
+      <c r="N489" s="2"/>
+      <c r="O489" s="2"/>
+      <c r="P489" s="2"/>
+      <c r="Q489" s="2"/>
+      <c r="R489" s="2"/>
+      <c r="S489" s="2"/>
+      <c r="T489" s="2"/>
+      <c r="U489" s="2"/>
+      <c r="V489" s="2"/>
+      <c r="W489" s="2"/>
+      <c r="X489" s="2"/>
+      <c r="Y489" s="2"/>
+    </row>
+    <row r="490" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A490" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B489" s="3" t="s">
+      <c r="B490" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C489" s="4" t="s">
+      <c r="C490" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D489" s="3" t="s">
+      <c r="D490" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="E489" s="1"/>
-      <c r="F489" s="1"/>
-      <c r="G489" s="1"/>
-      <c r="H489" s="1"/>
-      <c r="I489" s="1"/>
-      <c r="J489" s="1"/>
-      <c r="K489" s="1"/>
-      <c r="L489" s="1"/>
-      <c r="M489" s="1"/>
-      <c r="N489" s="1"/>
-      <c r="O489" s="1"/>
-      <c r="P489" s="1"/>
-      <c r="Q489" s="1"/>
-      <c r="R489" s="1"/>
-      <c r="S489" s="1"/>
-      <c r="T489" s="1"/>
-      <c r="U489" s="1"/>
-      <c r="V489" s="1"/>
-      <c r="W489" s="1"/>
-      <c r="X489" s="1"/>
-      <c r="Y489" s="1"/>
-    </row>
-    <row r="490" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A490" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="B490" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="C490" s="47" t="s">
-        <v>715</v>
-      </c>
-      <c r="D490" s="5" t="s">
-        <v>716</v>
       </c>
       <c r="E490" s="1"/>
       <c r="F490" s="1"/>
@@ -21994,14 +22002,16 @@
     </row>
     <row r="491" spans="1:25" ht="15.75" customHeight="1">
       <c r="A491" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="B491" s="5"/>
-      <c r="C491" s="6" t="s">
-        <v>718</v>
+        <v>713</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C491" s="47" t="s">
+        <v>715</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E491" s="1"/>
       <c r="F491" s="1"/>
@@ -22026,942 +22036,969 @@
       <c r="Y491" s="1"/>
     </row>
     <row r="492" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A492" s="3" t="s">
+      <c r="A492" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B492" s="5"/>
+      <c r="C492" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="D492" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E492" s="1"/>
+      <c r="F492" s="1"/>
+      <c r="G492" s="1"/>
+      <c r="H492" s="1"/>
+      <c r="I492" s="1"/>
+      <c r="J492" s="1"/>
+      <c r="K492" s="1"/>
+      <c r="L492" s="1"/>
+      <c r="M492" s="1"/>
+      <c r="N492" s="1"/>
+      <c r="O492" s="1"/>
+      <c r="P492" s="1"/>
+      <c r="Q492" s="1"/>
+      <c r="R492" s="1"/>
+      <c r="S492" s="1"/>
+      <c r="T492" s="1"/>
+      <c r="U492" s="1"/>
+      <c r="V492" s="1"/>
+      <c r="W492" s="1"/>
+      <c r="X492" s="1"/>
+      <c r="Y492" s="1"/>
+    </row>
+    <row r="493" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A493" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="B492" s="3" t="s">
+      <c r="B493" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="C492" s="3" t="s">
+      <c r="C493" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="D492" s="3" t="s">
+      <c r="D493" s="3" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="493" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A493" s="9" t="s">
+    <row r="494" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A494" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="B493" s="9" t="s">
+      <c r="B494" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="C493" s="11" t="s">
+      <c r="C494" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="D493" s="9" t="s">
+      <c r="D494" s="9" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="494" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A494" s="3" t="s">
+    <row r="495" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A495" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B494" s="3" t="s">
+      <c r="B495" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C494" s="4" t="s">
+      <c r="C495" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="D494" s="3" t="s">
+      <c r="D495" s="3" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="495" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A495" s="5" t="s">
+    <row r="496" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A496" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="B495" s="5"/>
-      <c r="C495" s="47" t="s">
+      <c r="B496" s="5"/>
+      <c r="C496" s="47" t="s">
         <v>729</v>
       </c>
-      <c r="D495" s="5" t="s">
+      <c r="D496" s="5" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="496" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A496" s="90" t="s">
+    <row r="497" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A497" s="90" t="s">
         <v>1438</v>
       </c>
-      <c r="B496" s="90"/>
-      <c r="C496" s="91" t="s">
+      <c r="B497" s="90"/>
+      <c r="C497" s="91" t="s">
         <v>1439</v>
       </c>
-      <c r="D496" s="90" t="s">
+      <c r="D497" s="90" t="s">
         <v>1440</v>
       </c>
     </row>
-    <row r="497" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A497" s="3" t="s">
+    <row r="498" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A498" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B497" s="3"/>
-      <c r="C497" s="3" t="s">
+      <c r="B498" s="3"/>
+      <c r="C498" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="D497" s="3" t="s">
+      <c r="D498" s="3" t="s">
         <v>730</v>
-      </c>
-    </row>
-    <row r="498" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A498" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="B498" s="9"/>
-      <c r="C498" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="D498" s="9" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="499" spans="1:4" ht="15.75" customHeight="1">
       <c r="A499" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="B499" s="9" t="s">
-        <v>735</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="B499" s="9"/>
       <c r="C499" s="10" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D499" s="9" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="500" spans="1:4" ht="15.75" customHeight="1">
       <c r="A500" s="9" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B500" s="9"/>
-      <c r="C500" s="52" t="s">
-        <v>1157</v>
+        <v>734</v>
+      </c>
+      <c r="B500" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="C500" s="10" t="s">
+        <v>736</v>
       </c>
       <c r="D500" s="9" t="s">
-        <v>1158</v>
+        <v>734</v>
       </c>
     </row>
     <row r="501" spans="1:4" ht="15.75" customHeight="1">
       <c r="A501" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B501" s="9"/>
+      <c r="C501" s="52" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D501" s="9" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A502" s="9" t="s">
         <v>1159</v>
       </c>
-      <c r="B501" s="9"/>
-      <c r="C501" s="10" t="s">
+      <c r="B502" s="9"/>
+      <c r="C502" s="10" t="s">
         <v>1161</v>
       </c>
-      <c r="D501" s="9" t="s">
+      <c r="D502" s="9" t="s">
         <v>1160</v>
-      </c>
-    </row>
-    <row r="502" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A502" s="90" t="s">
-        <v>1441</v>
-      </c>
-      <c r="B502" s="90"/>
-      <c r="C502" s="91" t="s">
-        <v>1442</v>
-      </c>
-      <c r="D502" s="90" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="503" spans="1:4" ht="15.75" customHeight="1">
       <c r="A503" s="90" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B503" s="90"/>
       <c r="C503" s="91" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D503" s="90" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A504" s="90" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B504" s="90"/>
+      <c r="C504" s="91" t="s">
         <v>1444</v>
       </c>
-      <c r="D503" s="90" t="s">
+      <c r="D504" s="90" t="s">
         <v>1443</v>
       </c>
     </row>
-    <row r="504" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A504" s="5" t="s">
+    <row r="505" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A505" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B504" s="5" t="s">
+      <c r="B505" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C504" s="47" t="s">
+      <c r="C505" s="47" t="s">
         <v>739</v>
       </c>
-      <c r="D504" s="5" t="s">
+      <c r="D505" s="5" t="s">
         <v>737</v>
-      </c>
-    </row>
-    <row r="505" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A505" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="B505" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C505" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D505" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="506" spans="1:4" ht="15.75" customHeight="1">
       <c r="A506" s="3" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B506" s="3"/>
+        <v>740</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>741</v>
+      </c>
       <c r="C506" s="3" t="s">
-        <v>1294</v>
+        <v>742</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>1293</v>
+        <v>740</v>
       </c>
     </row>
     <row r="507" spans="1:4" ht="15.75" customHeight="1">
       <c r="A507" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B507" s="3"/>
+      <c r="C507" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D507" s="3" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A508" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B507" s="3" t="s">
+      <c r="B508" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="C507" s="3" t="s">
+      <c r="C508" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="D507" s="3" t="s">
+      <c r="D508" s="3" t="s">
         <v>743</v>
-      </c>
-    </row>
-    <row r="508" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A508" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="B508" s="5"/>
-      <c r="C508" s="6" t="s">
-        <v>746</v>
-      </c>
-      <c r="D508" s="5" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="509" spans="1:4" ht="15.75" customHeight="1">
       <c r="A509" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B509" s="5"/>
+      <c r="C509" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D509" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A510" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B509" s="5" t="s">
+      <c r="B510" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C509" s="30" t="s">
+      <c r="C510" s="30" t="s">
         <v>750</v>
       </c>
-      <c r="D509" s="5" t="s">
+      <c r="D510" s="5" t="s">
         <v>748</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A510" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B510" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C510" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D510" s="3" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="511" spans="1:4" ht="15.75" customHeight="1">
       <c r="A511" s="3" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B511" s="3"/>
+        <v>751</v>
+      </c>
+      <c r="B511" s="3" t="s">
+        <v>752</v>
+      </c>
       <c r="C511" s="3" t="s">
-        <v>1163</v>
+        <v>753</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>1162</v>
+        <v>751</v>
       </c>
     </row>
     <row r="512" spans="1:4" ht="15.75" customHeight="1">
       <c r="A512" s="3" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B512" s="3"/>
       <c r="C512" s="3" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="513" spans="1:4" ht="15.75" customHeight="1">
       <c r="A513" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B513" s="3"/>
+      <c r="C513" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D513" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A514" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="B513" s="3" t="s">
+      <c r="B514" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="C513" s="3" t="s">
+      <c r="C514" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="D513" s="3" t="s">
+      <c r="D514" s="3" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="514" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A514" s="5" t="s">
+    <row r="515" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A515" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B514" s="5" t="s">
+      <c r="B515" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="C514" s="6" t="s">
+      <c r="C515" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="D514" s="5" t="s">
+      <c r="D515" s="5" t="s">
         <v>757</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A515" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="B515" s="7"/>
-      <c r="C515" s="31" t="s">
-        <v>761</v>
-      </c>
-      <c r="D515" s="7" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="516" spans="1:4" ht="15.75" customHeight="1">
       <c r="A516" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B516" s="7"/>
+      <c r="C516" s="31" t="s">
+        <v>761</v>
+      </c>
+      <c r="D516" s="7" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A517" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="B516" s="7" t="s">
+      <c r="B517" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C516" s="31" t="s">
+      <c r="C517" s="31" t="s">
         <v>1169</v>
       </c>
-      <c r="D516" s="7" t="s">
+      <c r="D517" s="7" t="s">
         <v>1167</v>
-      </c>
-    </row>
-    <row r="517" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A517" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B517" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C517" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="518" spans="1:4" ht="15.75" customHeight="1">
       <c r="A518" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B518" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D518" s="1" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A519" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B518" s="3" t="s">
+      <c r="B519" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C518" s="50" t="s">
+      <c r="C519" s="50" t="s">
         <v>765</v>
       </c>
-      <c r="D518" s="3" t="s">
+      <c r="D519" s="3" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="519" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A519" s="5" t="s">
+    <row r="520" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A520" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B519" s="5" t="s">
+      <c r="B520" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="C519" s="6" t="s">
+      <c r="C520" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D519" s="5" t="s">
+      <c r="D520" s="5" t="s">
         <v>769</v>
-      </c>
-    </row>
-    <row r="520" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A520" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B520" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="C520" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="D520" s="3" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="521" spans="1:4" ht="15.75" customHeight="1">
       <c r="A521" s="3" t="s">
-        <v>1170</v>
+        <v>770</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1171</v>
+        <v>771</v>
       </c>
       <c r="C521" s="4" t="s">
-        <v>1172</v>
+        <v>772</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>1173</v>
+        <v>770</v>
       </c>
     </row>
     <row r="522" spans="1:4" ht="15.75" customHeight="1">
       <c r="A522" s="3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B522" s="3"/>
+        <v>1170</v>
+      </c>
+      <c r="B522" s="3" t="s">
+        <v>1171</v>
+      </c>
       <c r="C522" s="4" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="523" spans="1:4" ht="15.75" customHeight="1">
       <c r="A523" s="3" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B523" s="3"/>
       <c r="C523" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D523" s="3" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A524" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B524" s="3"/>
+      <c r="C524" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="D523" s="3" t="s">
+      <c r="D524" s="3" t="s">
         <v>1181</v>
-      </c>
-    </row>
-    <row r="524" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A524" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="B524" s="9"/>
-      <c r="C524" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="D524" s="9" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="525" spans="1:4" ht="15.75" customHeight="1">
       <c r="A525" s="9" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B525" s="9" t="s">
-        <v>1183</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="B525" s="9"/>
       <c r="C525" s="11" t="s">
-        <v>1184</v>
+        <v>774</v>
       </c>
       <c r="D525" s="9" t="s">
-        <v>1183</v>
+        <v>773</v>
       </c>
     </row>
     <row r="526" spans="1:4" ht="15.75" customHeight="1">
       <c r="A526" s="9" t="s">
-        <v>775</v>
+        <v>1182</v>
       </c>
       <c r="B526" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="C526" s="10" t="s">
-        <v>777</v>
+        <v>1183</v>
+      </c>
+      <c r="C526" s="11" t="s">
+        <v>1184</v>
       </c>
       <c r="D526" s="9" t="s">
-        <v>775</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="527" spans="1:4" ht="15.75" customHeight="1">
       <c r="A527" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B527" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="C527" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="D527" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A528" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="B527" s="9"/>
-      <c r="C527" s="11" t="s">
+      <c r="B528" s="9"/>
+      <c r="C528" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="D527" s="9" t="s">
+      <c r="D528" s="9" t="s">
         <v>780</v>
-      </c>
-    </row>
-    <row r="528" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A528" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="B528" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C528" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D528" s="7" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="529" spans="1:4" ht="15.75" customHeight="1">
       <c r="A529" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B529" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C529" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D529" s="7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A530" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="B529" s="7"/>
-      <c r="C529" s="8" t="s">
+      <c r="B530" s="7"/>
+      <c r="C530" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="D529" s="7" t="s">
+      <c r="D530" s="7" t="s">
         <v>781</v>
-      </c>
-    </row>
-    <row r="530" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A530" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="B530" s="5"/>
-      <c r="C530" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="D530" s="5" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="531" spans="1:4" ht="15.75" customHeight="1">
       <c r="A531" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B531" s="5" t="s">
-        <v>1186</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="B531" s="5"/>
       <c r="C531" s="6" t="s">
-        <v>1185</v>
+        <v>791</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>1188</v>
+        <v>790</v>
       </c>
     </row>
     <row r="532" spans="1:4" ht="15.75" customHeight="1">
       <c r="A532" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B532" s="5"/>
+        <v>1187</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>1186</v>
+      </c>
       <c r="C532" s="6" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D532" s="5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="533" spans="1:4" ht="15.75" customHeight="1">
       <c r="A533" s="5" t="s">
-        <v>792</v>
+        <v>1189</v>
       </c>
       <c r="B533" s="5"/>
       <c r="C533" s="6" t="s">
-        <v>793</v>
+        <v>1190</v>
       </c>
       <c r="D533" s="5" t="s">
-        <v>794</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="534" spans="1:4" ht="15.75" customHeight="1">
       <c r="A534" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B534" s="5"/>
       <c r="C534" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D534" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="535" spans="1:4" ht="15.75" customHeight="1">
       <c r="A535" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B535" s="5"/>
       <c r="C535" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D535" s="5" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="536" spans="1:4" ht="15.75" customHeight="1">
       <c r="A536" s="5" t="s">
-        <v>1191</v>
+        <v>797</v>
       </c>
       <c r="B536" s="5"/>
       <c r="C536" s="6" t="s">
-        <v>1192</v>
+        <v>798</v>
       </c>
       <c r="D536" s="5" t="s">
-        <v>1191</v>
+        <v>799</v>
       </c>
     </row>
     <row r="537" spans="1:4" ht="15.75" customHeight="1">
       <c r="A537" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B537" s="5" t="s">
-        <v>801</v>
-      </c>
+        <v>1191</v>
+      </c>
+      <c r="B537" s="5"/>
       <c r="C537" s="6" t="s">
-        <v>802</v>
+        <v>1192</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>803</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="538" spans="1:4" ht="15.75" customHeight="1">
       <c r="A538" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="C538" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="D538" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A539" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B538" s="5"/>
-      <c r="C538" s="6" t="s">
+      <c r="B539" s="5"/>
+      <c r="C539" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="D538" s="5" t="s">
+      <c r="D539" s="5" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="539" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A539" s="7" t="s">
+    <row r="540" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A540" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B539" s="7"/>
-      <c r="C539" s="8" t="s">
+      <c r="B540" s="7"/>
+      <c r="C540" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="D539" s="7" t="s">
+      <c r="D540" s="7" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="540" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A540" s="5" t="s">
+    <row r="541" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A541" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B540" s="5"/>
-      <c r="C540" s="6" t="s">
+      <c r="B541" s="5"/>
+      <c r="C541" s="6" t="s">
         <v>810</v>
       </c>
-      <c r="D540" s="5" t="s">
+      <c r="D541" s="5" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="541" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A541" s="90" t="s">
+    <row r="542" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A542" s="90" t="s">
         <v>1445</v>
       </c>
-      <c r="B541" s="90"/>
-      <c r="C541" s="91" t="s">
+      <c r="B542" s="90"/>
+      <c r="C542" s="91" t="s">
         <v>1446</v>
       </c>
-      <c r="D541" s="90" t="s">
+      <c r="D542" s="90" t="s">
         <v>1445</v>
       </c>
     </row>
-    <row r="542" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A542" s="3" t="s">
+    <row r="543" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A543" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="B542" s="3" t="s">
+      <c r="B543" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="C542" s="3" t="s">
+      <c r="C543" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="D542" s="1" t="s">
+      <c r="D543" s="1" t="s">
         <v>1021</v>
-      </c>
-    </row>
-    <row r="543" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A543" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="B543" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="C543" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="D543" s="5" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="544" spans="1:4" ht="15.75" customHeight="1">
       <c r="A544" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C544" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D544" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A545" s="5" t="s">
         <v>1295</v>
       </c>
-      <c r="B544" s="5" t="s">
+      <c r="B545" s="5" t="s">
         <v>1296</v>
       </c>
-      <c r="C544" s="6" t="s">
+      <c r="C545" s="6" t="s">
         <v>1297</v>
       </c>
-      <c r="D544" s="5" t="s">
+      <c r="D545" s="5" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="545" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A545" s="90" t="s">
+    <row r="546" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A546" s="90" t="s">
         <v>1447</v>
       </c>
-      <c r="B545" s="90"/>
-      <c r="C545" s="91" t="s">
+      <c r="B546" s="90"/>
+      <c r="C546" s="91" t="s">
         <v>1448</v>
       </c>
-      <c r="D545" s="90" t="s">
+      <c r="D546" s="90" t="s">
         <v>1447</v>
-      </c>
-    </row>
-    <row r="546" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A546" s="3" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B546" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C546" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D546" s="1" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="547" spans="1:4" ht="15.75" customHeight="1">
       <c r="A547" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B547" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D547" s="1" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A548" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B547" s="3"/>
-      <c r="C547" s="50" t="s">
+      <c r="B548" s="3"/>
+      <c r="C548" s="50" t="s">
         <v>815</v>
       </c>
-      <c r="D547" s="3" t="s">
+      <c r="D548" s="3" t="s">
         <v>814</v>
-      </c>
-    </row>
-    <row r="548" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A548" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="B548" s="9"/>
-      <c r="C548" s="10" t="s">
-        <v>817</v>
-      </c>
-      <c r="D548" s="9" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="549" spans="1:4" ht="15.75" customHeight="1">
       <c r="A549" s="9" t="s">
-        <v>1298</v>
+        <v>816</v>
       </c>
       <c r="B549" s="9"/>
       <c r="C549" s="10" t="s">
-        <v>1299</v>
+        <v>817</v>
       </c>
       <c r="D549" s="9" t="s">
-        <v>1298</v>
+        <v>818</v>
       </c>
     </row>
     <row r="550" spans="1:4" ht="15.75" customHeight="1">
       <c r="A550" s="9" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B550" s="9"/>
+      <c r="C550" s="10" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D550" s="9" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A551" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="B550" s="9" t="s">
+      <c r="B551" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="C550" s="11" t="s">
+      <c r="C551" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="D550" s="9" t="s">
+      <c r="D551" s="9" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="551" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A551" s="7" t="s">
+    <row r="552" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A552" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="B551" s="7" t="s">
+      <c r="B552" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="C551" s="53" t="s">
+      <c r="C552" s="53" t="s">
         <v>925</v>
       </c>
-      <c r="D551" s="7" t="s">
+      <c r="D552" s="7" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="552" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A552" s="109" t="s">
+    <row r="553" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A553" s="109" t="s">
         <v>1496</v>
       </c>
-      <c r="B552" s="109"/>
-      <c r="C552" s="110" t="s">
+      <c r="B553" s="109"/>
+      <c r="C553" s="110" t="s">
         <v>1497</v>
       </c>
-      <c r="D552" s="109" t="s">
+      <c r="D553" s="109" t="s">
         <v>1496</v>
-      </c>
-    </row>
-    <row r="553" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A553" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B553" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C553" s="50" t="s">
-        <v>824</v>
-      </c>
-      <c r="D553" s="3" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="554" spans="1:4" ht="15.75" customHeight="1">
       <c r="A554" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B554" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C554" s="50" t="s">
+        <v>824</v>
+      </c>
+      <c r="D554" s="3" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A555" s="3" t="s">
         <v>1300</v>
       </c>
-      <c r="B554" s="3" t="s">
+      <c r="B555" s="3" t="s">
         <v>1301</v>
       </c>
-      <c r="C554" s="50" t="s">
+      <c r="C555" s="50" t="s">
         <v>1302</v>
       </c>
-      <c r="D554" s="3" t="s">
+      <c r="D555" s="3" t="s">
         <v>1300</v>
       </c>
     </row>
-    <row r="555" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A555" s="9" t="s">
+    <row r="556" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A556" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="B555" s="9" t="s">
+      <c r="B556" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="C555" s="10" t="s">
+      <c r="C556" s="10" t="s">
         <v>827</v>
       </c>
-      <c r="D555" s="9" t="s">
+      <c r="D556" s="9" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="556" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A556" s="3" t="s">
+    <row r="557" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A557" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B556" s="3"/>
-      <c r="C556" s="4" t="s">
+      <c r="B557" s="3"/>
+      <c r="C557" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="D556" s="3" t="s">
+      <c r="D557" s="3" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="557" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A557" s="5" t="s">
+    <row r="558" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A558" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="B557" s="5"/>
-      <c r="C557" s="6" t="s">
+      <c r="B558" s="5"/>
+      <c r="C558" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="D557" s="48" t="s">
+      <c r="D558" s="48" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="558" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A558" s="3" t="s">
+    <row r="559" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A559" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="B558" s="3" t="s">
+      <c r="B559" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="C558" s="12" t="s">
+      <c r="C559" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="D558" s="1" t="s">
+      <c r="D559" s="1" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="559" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A559" s="5" t="s">
+    <row r="560" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A560" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="B559" s="5"/>
-      <c r="C559" s="6" t="s">
+      <c r="B560" s="5"/>
+      <c r="C560" s="6" t="s">
         <v>836</v>
       </c>
-      <c r="D559" s="49" t="s">
+      <c r="D560" s="49" t="s">
         <v>837</v>
-      </c>
-    </row>
-    <row r="560" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A560" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B560" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C560" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D560" s="1" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="561" spans="1:4" ht="15.75" customHeight="1">
       <c r="A561" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B561" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D561" s="1" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A562" s="3" t="s">
         <v>1303</v>
       </c>
-      <c r="B561" s="3"/>
-      <c r="C561" s="3" t="s">
+      <c r="B562" s="3"/>
+      <c r="C562" s="3" t="s">
         <v>1305</v>
       </c>
-      <c r="D561" s="1" t="s">
+      <c r="D562" s="1" t="s">
         <v>1304</v>
       </c>
     </row>
-    <row r="562" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A562" s="7" t="s">
+    <row r="563" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A563" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="B562" s="7" t="s">
+      <c r="B563" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="C562" s="68" t="s">
+      <c r="C563" s="68" t="s">
         <v>928</v>
       </c>
-      <c r="D562" s="69" t="s">
+      <c r="D563" s="69" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="563" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A563" s="90" t="s">
+    <row r="564" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A564" s="90" t="s">
         <v>1449</v>
       </c>
-      <c r="B563" s="90"/>
-      <c r="C563" s="91" t="s">
+      <c r="B564" s="90"/>
+      <c r="C564" s="91" t="s">
         <v>1450</v>
       </c>
-      <c r="D563" s="90" t="s">
+      <c r="D564" s="90" t="s">
         <v>1451</v>
       </c>
-    </row>
-    <row r="564" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A564" s="3"/>
-      <c r="B564" s="3"/>
-      <c r="C564" s="3"/>
-      <c r="D564" s="1"/>
     </row>
     <row r="565" spans="1:4" ht="15.75" customHeight="1">
       <c r="A565" s="3"/>
@@ -28134,6 +28171,12 @@
       <c r="B1426" s="3"/>
       <c r="C1426" s="3"/>
       <c r="D1426" s="1"/>
+    </row>
+    <row r="1427" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1427" s="3"/>
+      <c r="B1427" s="3"/>
+      <c r="C1427" s="3"/>
+      <c r="D1427" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -28323,49 +28366,49 @@
     <hyperlink ref="C452" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
     <hyperlink ref="C455" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
     <hyperlink ref="C458" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C471" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C472" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C472" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C473" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
     <hyperlink ref="C465" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
     <hyperlink ref="C466" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
     <hyperlink ref="C468" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C473" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C476" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C479" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C480" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C489" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C490" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C491" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C493" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C495" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C498" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C504" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C508" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C509" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C514" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C515" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C519" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C520" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C524" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C527" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C529" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C528" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C474" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C477" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C480" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C481" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C490" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C491" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C492" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C494" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C496" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C499" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C505" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C509" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C510" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C515" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C516" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C520" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C521" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C525" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C528" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C530" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C529" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C12" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C530" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C533" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C534" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C535" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C537" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C538" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C539" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C540" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C543" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C547" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C550" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C553" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C556" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C557" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C558" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C559" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C531" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C534" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C535" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C536" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C538" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C539" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C540" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C541" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C544" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C548" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C551" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C554" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C557" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C558" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C559" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C560" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="C245" r:id="rId230" xr:uid="{98DDE684-CC21-7C49-B22B-C4F92C88FD93}"/>
     <hyperlink ref="C327" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
     <hyperlink ref="C373" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
@@ -28393,8 +28436,8 @@
     <hyperlink ref="C439" r:id="rId254" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
     <hyperlink ref="C443" r:id="rId255" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
     <hyperlink ref="C456" r:id="rId256" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C551" r:id="rId257" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C562" r:id="rId258" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C552" r:id="rId257" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C563" r:id="rId258" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C271" r:id="rId259" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
     <hyperlink ref="C314" r:id="rId260" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
     <hyperlink ref="C243" r:id="rId261" xr:uid="{3DD3F81F-9B00-6C41-B9BD-0B246E4511FC}"/>
@@ -28414,10 +28457,10 @@
     <hyperlink ref="C207" r:id="rId275" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
     <hyperlink ref="C8" r:id="rId276" xr:uid="{B3656FCB-334A-C24F-B9FD-77A2E94511A7}"/>
     <hyperlink ref="C275" r:id="rId277" xr:uid="{8B707DBA-5046-0842-8A9D-B479BE7B3F26}"/>
-    <hyperlink ref="C500" r:id="rId278" xr:uid="{F0689FA1-BCC1-394B-AED5-B9A03C77A143}"/>
+    <hyperlink ref="C501" r:id="rId278" xr:uid="{F0689FA1-BCC1-394B-AED5-B9A03C77A143}"/>
     <hyperlink ref="C447" r:id="rId279" xr:uid="{6636B7ED-934A-D247-B837-6E7A652A0F48}"/>
     <hyperlink ref="C417" r:id="rId280" xr:uid="{27DBBE71-CF56-034F-A814-92AB6B007119}"/>
-    <hyperlink ref="C469" r:id="rId281" xr:uid="{65BB9F36-0658-5746-8674-E771C17EC4A1}"/>
+    <hyperlink ref="C470" r:id="rId281" xr:uid="{65BB9F36-0658-5746-8674-E771C17EC4A1}"/>
     <hyperlink ref="C3" r:id="rId282" xr:uid="{B66C9298-F7DC-4B4E-AAB0-9EE8349C9F1C}"/>
     <hyperlink ref="C9" r:id="rId283" xr:uid="{DC4D060D-57F7-0C44-9224-72CA0BA78162}"/>
     <hyperlink ref="C28" r:id="rId284" xr:uid="{19CEABC1-E5BB-1049-854F-4E4315DD70A2}"/>
@@ -28469,32 +28512,33 @@
     <hyperlink ref="C420" r:id="rId330" xr:uid="{6763A48D-7B18-E649-886C-08D461F9C515}"/>
     <hyperlink ref="C422" r:id="rId331" xr:uid="{FDF960AD-ED15-2749-AA75-EA51A85C1D97}"/>
     <hyperlink ref="C437" r:id="rId332" xr:uid="{86E669FB-1204-5549-9E6B-B0F1D2D62AF8}"/>
-    <hyperlink ref="C470" r:id="rId333" xr:uid="{3CEF2BDF-D127-3D4E-8E2B-EE75CD438AB1}"/>
-    <hyperlink ref="C474" r:id="rId334" xr:uid="{C7C34AC7-D6F1-4147-8650-1947BBC9693A}"/>
-    <hyperlink ref="C496" r:id="rId335" xr:uid="{119B456E-EC3C-F844-A9AD-61D4D0D2AFC3}"/>
-    <hyperlink ref="C502" r:id="rId336" xr:uid="{7E211C4E-5E81-EF40-84F3-839C934125D6}"/>
-    <hyperlink ref="C503" r:id="rId337" xr:uid="{8F44069E-D100-9645-8AB2-4DB0E187F4B3}"/>
-    <hyperlink ref="C541" r:id="rId338" xr:uid="{BF5A6084-E948-3645-A67B-5D86F56ECA88}"/>
-    <hyperlink ref="C545" r:id="rId339" xr:uid="{5AAAF9CF-4460-B54B-88C3-4A48BF9440D1}"/>
-    <hyperlink ref="C563" r:id="rId340" xr:uid="{7FBAFA5F-205B-2047-B22D-48C7875A450E}"/>
+    <hyperlink ref="C471" r:id="rId333" xr:uid="{3CEF2BDF-D127-3D4E-8E2B-EE75CD438AB1}"/>
+    <hyperlink ref="C475" r:id="rId334" xr:uid="{C7C34AC7-D6F1-4147-8650-1947BBC9693A}"/>
+    <hyperlink ref="C497" r:id="rId335" xr:uid="{119B456E-EC3C-F844-A9AD-61D4D0D2AFC3}"/>
+    <hyperlink ref="C503" r:id="rId336" xr:uid="{7E211C4E-5E81-EF40-84F3-839C934125D6}"/>
+    <hyperlink ref="C504" r:id="rId337" xr:uid="{8F44069E-D100-9645-8AB2-4DB0E187F4B3}"/>
+    <hyperlink ref="C542" r:id="rId338" xr:uid="{BF5A6084-E948-3645-A67B-5D86F56ECA88}"/>
+    <hyperlink ref="C546" r:id="rId339" xr:uid="{5AAAF9CF-4460-B54B-88C3-4A48BF9440D1}"/>
+    <hyperlink ref="C564" r:id="rId340" xr:uid="{7FBAFA5F-205B-2047-B22D-48C7875A450E}"/>
     <hyperlink ref="C350" r:id="rId341" xr:uid="{20FF35A0-9072-C349-94BD-F07C44AE26C4}"/>
-    <hyperlink ref="C518" r:id="rId342" xr:uid="{494AF78A-1E67-9744-B143-9F0F78B10E88}"/>
+    <hyperlink ref="C519" r:id="rId342" xr:uid="{494AF78A-1E67-9744-B143-9F0F78B10E88}"/>
     <hyperlink ref="C298" r:id="rId343" xr:uid="{C9BBF0C7-EF54-7043-A3FA-B4E339DB0706}"/>
     <hyperlink ref="C115" r:id="rId344" xr:uid="{3D770076-4E24-9D42-BFD9-96973B309E8D}"/>
     <hyperlink ref="C164" r:id="rId345" xr:uid="{EA7591F7-0A9D-634B-99CF-1BB6CB38CA70}"/>
-    <hyperlink ref="C488" r:id="rId346" xr:uid="{35D6A584-58BC-004E-A260-57FF94B25DE3}"/>
-    <hyperlink ref="C475" r:id="rId347" xr:uid="{B56C44DD-8FDA-1541-8C53-B0BDC19ED285}"/>
+    <hyperlink ref="C489" r:id="rId346" xr:uid="{35D6A584-58BC-004E-A260-57FF94B25DE3}"/>
+    <hyperlink ref="C476" r:id="rId347" xr:uid="{B56C44DD-8FDA-1541-8C53-B0BDC19ED285}"/>
     <hyperlink ref="C105" r:id="rId348" xr:uid="{797FFF51-AA26-DE45-9668-E68E19526507}"/>
     <hyperlink ref="C148" r:id="rId349" xr:uid="{2B42CB26-7EB6-214B-91FD-B36BA7CE2528}"/>
     <hyperlink ref="C282" r:id="rId350" xr:uid="{0864E2CB-03E9-574F-83E2-FC76D1C1CA3C}"/>
     <hyperlink ref="C289" r:id="rId351" xr:uid="{A7615311-ACEB-6541-8508-49DEF461E9E0}"/>
     <hyperlink ref="C339" r:id="rId352" xr:uid="{BA256D8A-594B-2F4F-BAFA-625867390502}"/>
-    <hyperlink ref="C552" r:id="rId353" xr:uid="{EBD10CF3-C016-274B-A7F0-1CBEDFD40D98}"/>
+    <hyperlink ref="C553" r:id="rId353" xr:uid="{EBD10CF3-C016-274B-A7F0-1CBEDFD40D98}"/>
+    <hyperlink ref="C469" r:id="rId354" xr:uid="{01E9142F-89C0-7841-92AF-1F64C525441E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId354"/>
+    <tablePart r:id="rId355"/>
   </tableParts>
 </worksheet>
 </file>
